--- a/data/processed/positivacao/2023-05_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-05_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25413,7 +25413,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B965" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr"/>
@@ -65709,7 +65709,7 @@
     <row r="2516">
       <c r="A2516" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2516" t="inlineStr"/>
@@ -67380,12 +67380,12 @@
       <c r="A2581" t="inlineStr"/>
       <c r="B2581" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 1.666,88
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 1.666,88
 Vendedor 18 - LOJA: positivou 140 cliente(s), não positivou 726 cliente(s) - Total vendido: R$ 60.413,05
-Vendedor 3 - FERNANDA: positivou 108 cliente(s), não positivou 336 cliente(s) - Total vendido: R$ 122.423,03
-Vendedor 4 - DANIELA: positivou 73 cliente(s), não positivou 583 cliente(s) - Total vendido: R$ 40.604,17
+Vendedor 3 - VENDEDOR 03: positivou 108 cliente(s), não positivou 336 cliente(s) - Total vendido: R$ 122.423,03
+Vendedor 4 - VENDEDOR 04: positivou 73 cliente(s), não positivou 583 cliente(s) - Total vendido: R$ 40.604,17
 Vendedor 5 - SITE: positivou 7 cliente(s), não positivou 441 cliente(s) - Total vendido: R$ 730,61
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2581" t="inlineStr"/>
